--- a/doc/단상 HMI 통신_4_2inch.xlsx
+++ b/doc/단상 HMI 통신_4_2inch.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevWork\4.IFTechWork\1.UPS1P1P\Display4.3\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419F75E3-37F0-4CD5-86EE-56EE78DAEED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243297E3-1AB1-4339-AF46-F720F9E8D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4_2inch 터치번지" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="210">
   <si>
     <t>정격 용량</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -588,202 +588,215 @@
     <t>17.14</t>
   </si>
   <si>
+    <t>16.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.2</t>
+  </si>
+  <si>
+    <t>16.3</t>
+  </si>
+  <si>
+    <t>16.4</t>
+  </si>
+  <si>
+    <t>16.5</t>
+  </si>
+  <si>
+    <t>16.6</t>
+  </si>
+  <si>
+    <t>16.7</t>
+  </si>
+  <si>
+    <t>16.8</t>
+  </si>
+  <si>
+    <t>16.9</t>
+  </si>
+  <si>
+    <t>16.10</t>
+  </si>
+  <si>
+    <t>16.11</t>
+  </si>
+  <si>
+    <t>16.12</t>
+  </si>
+  <si>
+    <t>16.13</t>
+  </si>
+  <si>
+    <t>16.14</t>
+  </si>
+  <si>
+    <t>16.15</t>
+  </si>
+  <si>
+    <t>15.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.2</t>
+  </si>
+  <si>
+    <t>15.3</t>
+  </si>
+  <si>
+    <t>15.4</t>
+  </si>
+  <si>
+    <t>15.5</t>
+  </si>
+  <si>
+    <t>15.6</t>
+  </si>
+  <si>
+    <t>15.7</t>
+  </si>
+  <si>
+    <t>15.8</t>
+  </si>
+  <si>
+    <t>15.9</t>
+  </si>
+  <si>
+    <t>15.10</t>
+  </si>
+  <si>
+    <t>15.11</t>
+  </si>
+  <si>
+    <t>15.12</t>
+  </si>
+  <si>
+    <t>15.13</t>
+  </si>
+  <si>
+    <t>15.14</t>
+  </si>
+  <si>
+    <t>15.15</t>
+  </si>
+  <si>
+    <t>6,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPS 내부 온도</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>###[도]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>vdc_link_volt_offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMMAND : Page_COMMAND == 6 [6 ~ 7],  FUNCTION CODE=0X06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SETUP : Page_Setup == 8 [8 ~ 14],  FUNCTION CODE=0X06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INTRO : Page_INTRO == 0 [0 ~ 5],  FUNCTION CODE=0X04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL 이벤트만 기록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7초 Latch(경보, 이벤트)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5초 Latch(경보, 이벤트)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALARM : Page_ALARM == 15 [15 ~ 20],  FUNCTION CODE=0X04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEASUREMENT : Page_MEASURE == 20 [20 ~ 37],  FUNCTION CODE=0X04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Measure_GAIN : Page_GAIN ==38 [38 ~ 49],  FUNCTION CODE=0X04, 06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Measure OFFSET : Page_OFFSET == 50 [50 ~ 58],  FUNCTION CODE=0X04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battery UV Primary Fault</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정내용(일반모드)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bat First UV Volt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80 - 280[Default = 120]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80 - 280[Default = 120]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인버터로 절환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반표준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고효율 표준(고효율로 출고 가능성없음 인증에 필요 메모리 사용안하고 모드 고정해서 사용함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출력 주파수로 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>output_frequency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OUTPUT CT ERR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출력 CT에러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>17.15</t>
-  </si>
-  <si>
-    <t>16.0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16.2</t>
-  </si>
-  <si>
-    <t>16.3</t>
-  </si>
-  <si>
-    <t>16.4</t>
-  </si>
-  <si>
-    <t>16.5</t>
-  </si>
-  <si>
-    <t>16.6</t>
-  </si>
-  <si>
-    <t>16.7</t>
-  </si>
-  <si>
-    <t>16.8</t>
-  </si>
-  <si>
-    <t>16.9</t>
-  </si>
-  <si>
-    <t>16.10</t>
-  </si>
-  <si>
-    <t>16.11</t>
-  </si>
-  <si>
-    <t>16.12</t>
-  </si>
-  <si>
-    <t>16.13</t>
-  </si>
-  <si>
-    <t>16.14</t>
-  </si>
-  <si>
-    <t>16.15</t>
-  </si>
-  <si>
-    <t>15.0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.2</t>
-  </si>
-  <si>
-    <t>15.3</t>
-  </si>
-  <si>
-    <t>15.4</t>
-  </si>
-  <si>
-    <t>15.5</t>
-  </si>
-  <si>
-    <t>15.6</t>
-  </si>
-  <si>
-    <t>15.7</t>
-  </si>
-  <si>
-    <t>15.8</t>
-  </si>
-  <si>
-    <t>15.9</t>
-  </si>
-  <si>
-    <t>15.10</t>
-  </si>
-  <si>
-    <t>15.11</t>
-  </si>
-  <si>
-    <t>15.12</t>
-  </si>
-  <si>
-    <t>15.13</t>
-  </si>
-  <si>
-    <t>15.14</t>
-  </si>
-  <si>
-    <t>15.15</t>
-  </si>
-  <si>
-    <t>6,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UPS 내부 온도</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>###[도]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>vdc_link_volt_offset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COMMAND : Page_COMMAND == 6 [6 ~ 7],  FUNCTION CODE=0X06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SETUP : Page_Setup == 8 [8 ~ 14],  FUNCTION CODE=0X06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INTRO : Page_INTRO == 0 [0 ~ 5],  FUNCTION CODE=0X04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALL 이벤트만 기록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7초 Latch(경보, 이벤트)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>5초 Latch(경보, 이벤트)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALARM : Page_ALARM == 15 [15 ~ 20],  FUNCTION CODE=0X04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MEASUREMENT : Page_MEASURE == 20 [20 ~ 37],  FUNCTION CODE=0X04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Measure_GAIN : Page_GAIN ==38 [38 ~ 49],  FUNCTION CODE=0X04, 06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Measure OFFSET : Page_OFFSET == 50 [50 ~ 58],  FUNCTION CODE=0X04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Battery UV Primary Fault</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수정내용(일반모드)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bat First UV Volt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>80 - 280[Default = 120]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>80 - 280[Default = 120]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인버터로 절환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반표준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고효율 표준(고효율로 출고 가능성없음 인증에 필요 메모리 사용안하고 모드 고정해서 사용함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>출력 주파수로 변경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>output_frequency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1: fault, 0: Normal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1509,6 +1522,45 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1516,9 +1568,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1541,42 +1590,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1903,21 +1916,21 @@
       <c r="B2" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="74"/>
+      <c r="D2" s="86"/>
       <c r="E2" s="20" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="41"/>
-      <c r="C3" s="75" t="s">
-        <v>189</v>
-      </c>
-      <c r="D3" s="75"/>
-      <c r="E3" s="76"/>
+      <c r="C3" s="87" t="s">
+        <v>188</v>
+      </c>
+      <c r="D3" s="87"/>
+      <c r="E3" s="88"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
@@ -1983,18 +1996,18 @@
     </row>
     <row r="9" spans="2:6" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B9" s="29"/>
-      <c r="C9" s="80" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="80"/>
-      <c r="E9" s="81"/>
+      <c r="C9" s="75" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="75"/>
+      <c r="E9" s="76"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="69">
+      <c r="B10" s="82">
         <v>6</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>129</v>
@@ -2004,7 +2017,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="70"/>
+      <c r="B11" s="83"/>
       <c r="C11" s="8">
         <v>6.1</v>
       </c>
@@ -2016,7 +2029,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="70"/>
+      <c r="B12" s="83"/>
       <c r="C12" s="8">
         <v>6.2</v>
       </c>
@@ -2026,7 +2039,7 @@
       <c r="E12" s="24"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="71"/>
+      <c r="B13" s="84"/>
       <c r="C13" s="8"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
@@ -2039,11 +2052,11 @@
     </row>
     <row r="15" spans="2:6" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B15" s="29"/>
-      <c r="C15" s="80" t="s">
-        <v>188</v>
-      </c>
-      <c r="D15" s="80"/>
-      <c r="E15" s="81"/>
+      <c r="C15" s="75" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15" s="75"/>
+      <c r="E15" s="76"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
@@ -2070,7 +2083,7 @@
         <v>22</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
@@ -2095,13 +2108,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E19" s="64" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2118,7 +2131,7 @@
         <v>58</v>
       </c>
       <c r="F20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2129,11 +2142,11 @@
     </row>
     <row r="22" spans="2:6" ht="28.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B22" s="34"/>
-      <c r="C22" s="77" t="s">
-        <v>193</v>
-      </c>
-      <c r="D22" s="78"/>
-      <c r="E22" s="79"/>
+      <c r="C22" s="89" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" s="90"/>
+      <c r="E22" s="91"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="1"/>
@@ -2144,15 +2157,15 @@
         <v>60</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="72">
+      <c r="B24" s="80">
         <v>15</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D24" s="25" t="s">
         <v>114</v>
@@ -2160,9 +2173,9 @@
       <c r="E24" s="26"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="72"/>
+      <c r="B25" s="80"/>
       <c r="C25" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D25" s="25" t="s">
         <v>115</v>
@@ -2170,9 +2183,9 @@
       <c r="E25" s="26"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="72"/>
+      <c r="B26" s="80"/>
       <c r="C26" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D26" s="25" t="s">
         <v>116</v>
@@ -2180,9 +2193,9 @@
       <c r="E26" s="26"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="72"/>
+      <c r="B27" s="80"/>
       <c r="C27" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D27" s="25" t="s">
         <v>127</v>
@@ -2190,9 +2203,9 @@
       <c r="E27" s="26"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="72"/>
+      <c r="B28" s="80"/>
       <c r="C28" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D28" s="25" t="s">
         <v>120</v>
@@ -2200,9 +2213,9 @@
       <c r="E28" s="26"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="72"/>
+      <c r="B29" s="80"/>
       <c r="C29" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D29" s="25" t="s">
         <v>121</v>
@@ -2210,9 +2223,9 @@
       <c r="E29" s="26"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="72"/>
+      <c r="B30" s="80"/>
       <c r="C30" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D30" s="25" t="s">
         <v>122</v>
@@ -2220,9 +2233,9 @@
       <c r="E30" s="26"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="72"/>
+      <c r="B31" s="80"/>
       <c r="C31" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D31" s="25" t="s">
         <v>126</v>
@@ -2230,9 +2243,9 @@
       <c r="E31" s="26"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="72"/>
+      <c r="B32" s="80"/>
       <c r="C32" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D32" s="25" t="s">
         <v>117</v>
@@ -2240,9 +2253,9 @@
       <c r="E32" s="26"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="72"/>
+      <c r="B33" s="80"/>
       <c r="C33" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D33" s="25" t="s">
         <v>118</v>
@@ -2250,9 +2263,9 @@
       <c r="E33" s="26"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="72"/>
+      <c r="B34" s="80"/>
       <c r="C34" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D34" s="25" t="s">
         <v>119</v>
@@ -2260,9 +2273,9 @@
       <c r="E34" s="26"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35" s="72"/>
+      <c r="B35" s="80"/>
       <c r="C35" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D35" s="25" t="s">
         <v>125</v>
@@ -2270,19 +2283,19 @@
       <c r="E35" s="26"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="72"/>
+      <c r="B36" s="80"/>
       <c r="C36" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E36" s="26"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="80"/>
+      <c r="C37" s="15" t="s">
         <v>179</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="E36" s="26"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="72"/>
-      <c r="C37" s="15" t="s">
-        <v>180</v>
       </c>
       <c r="D37" s="25" t="s">
         <v>123</v>
@@ -2290,9 +2303,9 @@
       <c r="E37" s="26"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="72"/>
+      <c r="B38" s="80"/>
       <c r="C38" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D38" s="25" t="s">
         <v>124</v>
@@ -2300,9 +2313,9 @@
       <c r="E38" s="26"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="85"/>
+      <c r="B39" s="81"/>
       <c r="C39" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="26"/>
@@ -2319,15 +2332,15 @@
         <v>3</v>
       </c>
       <c r="E40" s="39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="69">
+      <c r="B41" s="82">
         <v>16</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D41" s="27" t="s">
         <v>74</v>
@@ -2340,9 +2353,9 @@
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="72"/>
+      <c r="B42" s="80"/>
       <c r="C42" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D42" s="27" t="s">
         <v>66</v>
@@ -2355,9 +2368,9 @@
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B43" s="72"/>
+      <c r="B43" s="80"/>
       <c r="C43" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D43" s="27" t="s">
         <v>67</v>
@@ -2370,9 +2383,9 @@
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B44" s="72"/>
+      <c r="B44" s="80"/>
       <c r="C44" s="49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D44" s="50" t="s">
         <v>111</v>
@@ -2382,9 +2395,9 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B45" s="72"/>
+      <c r="B45" s="80"/>
       <c r="C45" s="49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D45" s="50" t="s">
         <v>77</v>
@@ -2394,9 +2407,9 @@
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="72"/>
+      <c r="B46" s="80"/>
       <c r="C46" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D46" s="27" t="s">
         <v>68</v>
@@ -2409,9 +2422,9 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="72"/>
+      <c r="B47" s="80"/>
       <c r="C47" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D47" s="27" t="s">
         <v>69</v>
@@ -2424,9 +2437,9 @@
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="72"/>
+      <c r="B48" s="80"/>
       <c r="C48" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D48" s="27" t="s">
         <v>70</v>
@@ -2439,9 +2452,9 @@
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="72"/>
+      <c r="B49" s="80"/>
       <c r="C49" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D49" s="27" t="s">
         <v>71</v>
@@ -2454,9 +2467,9 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B50" s="72"/>
+      <c r="B50" s="80"/>
       <c r="C50" s="49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D50" s="50" t="s">
         <v>112</v>
@@ -2466,9 +2479,9 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="72"/>
+      <c r="B51" s="80"/>
       <c r="C51" s="16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D51" s="27" t="s">
         <v>72</v>
@@ -2481,9 +2494,9 @@
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="72"/>
+      <c r="B52" s="80"/>
       <c r="C52" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D52" s="27" t="s">
         <v>73</v>
@@ -2496,9 +2509,9 @@
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B53" s="70"/>
+      <c r="B53" s="83"/>
       <c r="C53" s="54" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D53" s="55" t="s">
         <v>78</v>
@@ -2509,9 +2522,9 @@
       <c r="F53" s="36"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B54" s="70"/>
+      <c r="B54" s="83"/>
       <c r="C54" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D54" s="27" t="s">
         <v>80</v>
@@ -2521,9 +2534,9 @@
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="70"/>
+      <c r="B55" s="83"/>
       <c r="C55" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D55" s="27" t="s">
         <v>82</v>
@@ -2536,9 +2549,9 @@
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B56" s="71"/>
+      <c r="B56" s="84"/>
       <c r="C56" s="49" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D56" s="52" t="s">
         <v>61</v>
@@ -2556,11 +2569,11 @@
         <v>83</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B58" s="69">
+      <c r="B58" s="82">
         <v>17</v>
       </c>
       <c r="C58" s="16" t="s">
@@ -2577,7 +2590,7 @@
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="70"/>
+      <c r="B59" s="83"/>
       <c r="C59" s="16" t="s">
         <v>136</v>
       </c>
@@ -2592,7 +2605,7 @@
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B60" s="70"/>
+      <c r="B60" s="83"/>
       <c r="C60" s="16" t="s">
         <v>137</v>
       </c>
@@ -2607,7 +2620,7 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="70"/>
+      <c r="B61" s="83"/>
       <c r="C61" s="16" t="s">
         <v>138</v>
       </c>
@@ -2622,7 +2635,7 @@
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="70"/>
+      <c r="B62" s="83"/>
       <c r="C62" s="16" t="s">
         <v>139</v>
       </c>
@@ -2637,7 +2650,7 @@
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B63" s="70"/>
+      <c r="B63" s="83"/>
       <c r="C63" s="16" t="s">
         <v>140</v>
       </c>
@@ -2652,22 +2665,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B64" s="70"/>
+      <c r="B64" s="83"/>
       <c r="C64" s="57" t="s">
         <v>141</v>
       </c>
       <c r="D64" s="58" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E64" s="59" t="s">
         <v>75</v>
       </c>
       <c r="F64" s="60" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B65" s="70"/>
+      <c r="B65" s="83"/>
       <c r="C65" s="16" t="s">
         <v>142</v>
       </c>
@@ -2682,7 +2695,7 @@
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B66" s="70"/>
+      <c r="B66" s="83"/>
       <c r="C66" s="16" t="s">
         <v>143</v>
       </c>
@@ -2697,7 +2710,7 @@
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B67" s="70"/>
+      <c r="B67" s="83"/>
       <c r="C67" s="16" t="s">
         <v>144</v>
       </c>
@@ -2712,7 +2725,7 @@
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B68" s="70"/>
+      <c r="B68" s="83"/>
       <c r="C68" s="16" t="s">
         <v>145</v>
       </c>
@@ -2727,7 +2740,7 @@
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B69" s="70"/>
+      <c r="B69" s="83"/>
       <c r="C69" s="16" t="s">
         <v>146</v>
       </c>
@@ -2742,7 +2755,7 @@
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="70"/>
+      <c r="B70" s="83"/>
       <c r="C70" s="16" t="s">
         <v>147</v>
       </c>
@@ -2754,7 +2767,7 @@
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B71" s="70"/>
+      <c r="B71" s="83"/>
       <c r="C71" s="16" t="s">
         <v>148</v>
       </c>
@@ -2769,7 +2782,7 @@
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B72" s="70"/>
+      <c r="B72" s="83"/>
       <c r="C72" s="16" t="s">
         <v>149</v>
       </c>
@@ -2777,16 +2790,23 @@
         <v>85</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>75</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="73"/>
+      <c r="B73" s="85"/>
       <c r="C73" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="D73" s="30"/>
-      <c r="E73" s="28"/>
+        <v>208</v>
+      </c>
+      <c r="D73" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="E73" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="F73" s="35" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="74" spans="2:6" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B74" s="7"/>
@@ -2796,11 +2816,11 @@
     </row>
     <row r="75" spans="2:6" ht="28.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B75" s="29"/>
-      <c r="C75" s="80" t="s">
-        <v>194</v>
-      </c>
-      <c r="D75" s="80"/>
-      <c r="E75" s="81"/>
+      <c r="C75" s="75" t="s">
+        <v>193</v>
+      </c>
+      <c r="D75" s="75"/>
+      <c r="E75" s="76"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="4">
@@ -2956,24 +2976,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="2:7" s="91" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="87">
+    <row r="87" spans="2:7" s="74" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="70">
         <v>31</v>
       </c>
-      <c r="C87" s="88">
+      <c r="C87" s="71">
         <v>11</v>
       </c>
-      <c r="D87" s="89" t="s">
+      <c r="D87" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="E87" s="90" t="s">
+      <c r="E87" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="F87" s="86" t="s">
+      <c r="F87" s="69" t="s">
+        <v>204</v>
+      </c>
+      <c r="G87" s="74" t="s">
         <v>205</v>
-      </c>
-      <c r="G87" s="91" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
@@ -3012,10 +3032,10 @@
         <v>14</v>
       </c>
       <c r="D90" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="E90" s="26" t="s">
         <v>184</v>
-      </c>
-      <c r="E90" s="26" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="91" spans="2:7" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3026,11 +3046,11 @@
     </row>
     <row r="92" spans="2:7" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B92" s="29"/>
-      <c r="C92" s="82" t="s">
-        <v>195</v>
-      </c>
-      <c r="D92" s="83"/>
-      <c r="E92" s="84"/>
+      <c r="C92" s="77" t="s">
+        <v>194</v>
+      </c>
+      <c r="D92" s="78"/>
+      <c r="E92" s="79"/>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B93" s="1">
@@ -3169,11 +3189,11 @@
     <row r="103" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="104" spans="2:5" ht="27" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B104" s="29"/>
-      <c r="C104" s="80" t="s">
-        <v>196</v>
-      </c>
-      <c r="D104" s="80"/>
-      <c r="E104" s="81"/>
+      <c r="C104" s="75" t="s">
+        <v>195</v>
+      </c>
+      <c r="D104" s="75"/>
+      <c r="E104" s="76"/>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B105" s="4">
@@ -3211,7 +3231,7 @@
         <v>2</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E107" s="24" t="s">
         <v>43</v>
@@ -3302,11 +3322,6 @@
     <row r="114" spans="2:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="B24:B39"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="B41:B56"/>
     <mergeCell ref="B58:B73"/>
@@ -3314,6 +3329,11 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="B24:B39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/단상 HMI 통신_4_2inch.xlsx
+++ b/doc/단상 HMI 통신_4_2inch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevWork\4.IFTechWork\1.UPS1P1P\Display4.3\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243297E3-1AB1-4339-AF46-F720F9E8D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACEDEC81-2113-43D6-9705-F8BCF07E6B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4_2inch 터치번지" sheetId="2" r:id="rId1"/>
@@ -102,701 +102,702 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>###[V]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력 전압 :   ###[V]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력 전류 :  ###[A]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>직류링크 전압 :  ###[V]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>배터리 전압 :  ###[V]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>배터리 전류 :  ###[A]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>인버터 전압 :  ###[V]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>인버터 전류 :  ###[A]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>출력 전압 :  ###[V]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>출력 전류 :  ###[A]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력 주파수 :  ###[Hz]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>인버터 주파수 :  ###[Hz]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 - 500[Default = 250]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2 - 20[Default = 2]</t>
+  </si>
+  <si>
+    <t>100 - 240[Default = 220]</t>
+  </si>
+  <si>
+    <t>번지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input_volt_gain</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>offset 값 :   ####</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>input_volt_offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>input_current_offset</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bat_volt_offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bat_current_offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inverter_volt_offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inverter_current_offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>output_current_offset</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>inv_freqency</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bypass_freqency</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>바이패스 주파수 :  ###[Hz]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>부하율</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>###[V]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>###[%]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HF Mode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0: Normal, 1: High efficiency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10배수, ##.#[KVA]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Module state</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRANSFER RUN/STOP STATE</t>
+  </si>
+  <si>
+    <t>1: CONV ON, 0: CONV OFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1: DCDC ON, 0: DCDC OFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1: INV ON, 0: INV OFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1: INV MODE, 0: BYP MODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inverter OC(H/W Latch)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vdc_OV(H/W Latch)</t>
+  </si>
+  <si>
+    <t>Conv_GDU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inv_GDU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GDU_DCDC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Com_GDU</t>
+  </si>
+  <si>
+    <t>BAT_FUSE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Module OT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input_OC(H/W Latch)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1: fault, 0: Normal</t>
+  </si>
+  <si>
+    <t>1: fault, 0: Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC/DC CONVERTER RUN/STOP STATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buzz ON/OFF Control from COM.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">toggle : 부져정지 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EEPROM ERR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1: EEPROM Fault</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BAT MCCB Fault</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPS Operation Fault</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OFFSET CHECK ERR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL 정지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인버터 정지, 절환</t>
+  </si>
+  <si>
+    <t>인버터 정지, 절환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전기 정지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC/DC 정지</t>
+  </si>
+  <si>
+    <t>DC/DC 정지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>converter current limit fault(컨버터 전류제한이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vdc_link OV limit fault(직류링크 과전압 제한이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vdc_link UV limit fault(직류링크 저전압제한 이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>input under voltage fault(입력 저전압 이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>input over voltage fault(입력 고 전압 이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Input Frequency fault(입력 주파수 이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>utility line failure(정전)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battery current limit(배터리 전류제한 이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battery OV limit fault(배터리 과전압제한 이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battery UV limit fault(배터리 저전압제한 이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inverter output voltage fault(인버터 출력전압이상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>output OC overtime fault(출력 과부하)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inverter OL STOP(인버터 과부하 정지)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC/DC 정지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인버터 정지, 절환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인버터 정지, 절환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전기 정지, 인버터 정지, 절환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CONVERTER RUN/STOP STATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INVERTER RUN/STOP STATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충방전 모드 터치에서 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전부 운전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전부 재기동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전부 정지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인버터 운전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인버터 재 기동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">인버터 정지 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC/DC 운전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC/DC 재 기동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">DC/DC 정지 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바이패스 절환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상발생 바이패스 절환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상발생 인버터 정지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상발생 DC/DC 정지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상발생 충전기 정지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC/DC 정지(boost)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPS_ON_Command</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPS_OFF_Command</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Toggle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALARM RESET(알람 초기화)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배터리 정격전압</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배터리 용량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.2</t>
+  </si>
+  <si>
+    <t>17.3</t>
+  </si>
+  <si>
+    <t>17.4</t>
+  </si>
+  <si>
+    <t>17.5</t>
+  </si>
+  <si>
+    <t>17.6</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>17.8</t>
+  </si>
+  <si>
+    <t>17.9</t>
+  </si>
+  <si>
+    <t>17.10</t>
+  </si>
+  <si>
+    <t>17.11</t>
+  </si>
+  <si>
+    <t>17.12</t>
+  </si>
+  <si>
+    <t>17.13</t>
+  </si>
+  <si>
+    <t>17.14</t>
+  </si>
+  <si>
+    <t>16.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.2</t>
+  </si>
+  <si>
+    <t>16.3</t>
+  </si>
+  <si>
+    <t>16.4</t>
+  </si>
+  <si>
+    <t>16.5</t>
+  </si>
+  <si>
+    <t>16.6</t>
+  </si>
+  <si>
+    <t>16.7</t>
+  </si>
+  <si>
+    <t>16.8</t>
+  </si>
+  <si>
+    <t>16.9</t>
+  </si>
+  <si>
+    <t>16.10</t>
+  </si>
+  <si>
+    <t>16.11</t>
+  </si>
+  <si>
+    <t>16.12</t>
+  </si>
+  <si>
+    <t>16.13</t>
+  </si>
+  <si>
+    <t>16.14</t>
+  </si>
+  <si>
+    <t>16.15</t>
+  </si>
+  <si>
+    <t>15.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.2</t>
+  </si>
+  <si>
+    <t>15.3</t>
+  </si>
+  <si>
+    <t>15.4</t>
+  </si>
+  <si>
+    <t>15.5</t>
+  </si>
+  <si>
+    <t>15.6</t>
+  </si>
+  <si>
+    <t>15.7</t>
+  </si>
+  <si>
+    <t>15.8</t>
+  </si>
+  <si>
+    <t>15.9</t>
+  </si>
+  <si>
+    <t>15.10</t>
+  </si>
+  <si>
+    <t>15.11</t>
+  </si>
+  <si>
+    <t>15.12</t>
+  </si>
+  <si>
+    <t>15.13</t>
+  </si>
+  <si>
+    <t>15.14</t>
+  </si>
+  <si>
+    <t>15.15</t>
+  </si>
+  <si>
+    <t>6,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPS 내부 온도</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>###[도]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>vdc_link_volt_offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMMAND : Page_COMMAND == 6 [6 ~ 7],  FUNCTION CODE=0X06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SETUP : Page_Setup == 8 [8 ~ 14],  FUNCTION CODE=0X06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INTRO : Page_INTRO == 0 [0 ~ 5],  FUNCTION CODE=0X04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALL 이벤트만 기록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7초 Latch(경보, 이벤트)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5초 Latch(경보, 이벤트)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALARM : Page_ALARM == 15 [15 ~ 20],  FUNCTION CODE=0X04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEASUREMENT : Page_MEASURE == 20 [20 ~ 37],  FUNCTION CODE=0X04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Measure_GAIN : Page_GAIN ==38 [38 ~ 49],  FUNCTION CODE=0X04, 06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Measure OFFSET : Page_OFFSET == 50 [50 ~ 58],  FUNCTION CODE=0X04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battery UV Primary Fault</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정내용(일반모드)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bat First UV Volt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80 - 280[Default = 120]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80 - 280[Default = 120]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인버터로 절환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반표준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고효율 표준(고효율로 출고 가능성없음 인증에 필요 메모리 사용안하고 모드 고정해서 사용함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출력 주파수로 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>output_frequency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OUTPUT CT ERR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출력 CT에러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1: fault, 0: Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Output_voltage_ref</t>
-  </si>
-  <si>
-    <t>###[V]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>입력 전압 :   ###[V]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>입력 전류 :  ###[A]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>직류링크 전압 :  ###[V]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>배터리 전압 :  ###[V]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>배터리 전류 :  ###[A]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>인버터 전압 :  ###[V]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>인버터 전류 :  ###[A]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>출력 전압 :  ###[V]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>출력 전류 :  ###[A]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>입력 주파수 :  ###[Hz]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>인버터 주파수 :  ###[Hz]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0 - 500[Default = 250]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2 - 20[Default = 2]</t>
-  </si>
-  <si>
-    <t>100 - 240[Default = 220]</t>
-  </si>
-  <si>
-    <t>번지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>설명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>동작</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Input_volt_gain</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>offset 값 :   ####</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>input_volt_offset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>input_current_offset</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>bat_volt_offset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bat_current_offset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inverter_volt_offset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inverter_current_offset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>output_current_offset</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>inv_freqency</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>bypass_freqency</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>바이패스 주파수 :  ###[Hz]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>부하율</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>###[V]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>###[%]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HF Mode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0: Normal, 1: High efficiency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10배수, ##.#[KVA]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Module state</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TRANSFER RUN/STOP STATE</t>
-  </si>
-  <si>
-    <t>1: CONV ON, 0: CONV OFF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1: DCDC ON, 0: DCDC OFF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1: INV ON, 0: INV OFF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1: INV MODE, 0: BYP MODE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inverter OC(H/W Latch)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vdc_OV(H/W Latch)</t>
-  </si>
-  <si>
-    <t>Conv_GDU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inv_GDU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GDU_DCDC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Com_GDU</t>
-  </si>
-  <si>
-    <t>BAT_FUSE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Module OT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Input_OC(H/W Latch)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1: fault, 0: Normal</t>
-  </si>
-  <si>
-    <t>1: fault, 0: Normal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC/DC CONVERTER RUN/STOP STATE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buzz ON/OFF Control from COM.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">toggle : 부져정지 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EEPROM ERR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1: EEPROM Fault</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BAT MCCB Fault</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UPS Operation Fault</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OFFSET CHECK ERR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALL 정지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인버터 정지, 절환</t>
-  </si>
-  <si>
-    <t>인버터 정지, 절환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전기 정지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC/DC 정지</t>
-  </si>
-  <si>
-    <t>DC/DC 정지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>converter current limit fault(컨버터 전류제한이상)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vdc_link OV limit fault(직류링크 과전압 제한이상)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vdc_link UV limit fault(직류링크 저전압제한 이상)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>input under voltage fault(입력 저전압 이상)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>input over voltage fault(입력 고 전압 이상)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Input Frequency fault(입력 주파수 이상)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>utility line failure(정전)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>battery current limit(배터리 전류제한 이상)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Battery OV limit fault(배터리 과전압제한 이상)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>battery UV limit fault(배터리 저전압제한 이상)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inverter output voltage fault(인버터 출력전압이상)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>output OC overtime fault(출력 과부하)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>inverter OL STOP(인버터 과부하 정지)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC/DC 정지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인버터 정지, 절환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인버터 정지, 절환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALL STOP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전기 정지, 인버터 정지, 절환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALL STOP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CONVERTER RUN/STOP STATE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INVERTER RUN/STOP STATE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충방전 모드 터치에서 표시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전부 운전</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전부 재기동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전부 정지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인버터 운전</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인버터 재 기동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">인버터 정지 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC/DC 운전</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC/DC 재 기동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">DC/DC 정지 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>바이패스 절환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이상발생 바이패스 절환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이상발생 인버터 정지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이상발생 DC/DC 정지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이상발생 충전기 정지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC/DC 정지(boost)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UPS_ON_Command</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>UPS_OFF_Command</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Toggle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALARM RESET(알람 초기화)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>배터리 정격전압</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>배터리 용량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.2</t>
-  </si>
-  <si>
-    <t>17.3</t>
-  </si>
-  <si>
-    <t>17.4</t>
-  </si>
-  <si>
-    <t>17.5</t>
-  </si>
-  <si>
-    <t>17.6</t>
-  </si>
-  <si>
-    <t>17.7</t>
-  </si>
-  <si>
-    <t>17.8</t>
-  </si>
-  <si>
-    <t>17.9</t>
-  </si>
-  <si>
-    <t>17.10</t>
-  </si>
-  <si>
-    <t>17.11</t>
-  </si>
-  <si>
-    <t>17.12</t>
-  </si>
-  <si>
-    <t>17.13</t>
-  </si>
-  <si>
-    <t>17.14</t>
-  </si>
-  <si>
-    <t>16.0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16.2</t>
-  </si>
-  <si>
-    <t>16.3</t>
-  </si>
-  <si>
-    <t>16.4</t>
-  </si>
-  <si>
-    <t>16.5</t>
-  </si>
-  <si>
-    <t>16.6</t>
-  </si>
-  <si>
-    <t>16.7</t>
-  </si>
-  <si>
-    <t>16.8</t>
-  </si>
-  <si>
-    <t>16.9</t>
-  </si>
-  <si>
-    <t>16.10</t>
-  </si>
-  <si>
-    <t>16.11</t>
-  </si>
-  <si>
-    <t>16.12</t>
-  </si>
-  <si>
-    <t>16.13</t>
-  </si>
-  <si>
-    <t>16.14</t>
-  </si>
-  <si>
-    <t>16.15</t>
-  </si>
-  <si>
-    <t>15.0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.2</t>
-  </si>
-  <si>
-    <t>15.3</t>
-  </si>
-  <si>
-    <t>15.4</t>
-  </si>
-  <si>
-    <t>15.5</t>
-  </si>
-  <si>
-    <t>15.6</t>
-  </si>
-  <si>
-    <t>15.7</t>
-  </si>
-  <si>
-    <t>15.8</t>
-  </si>
-  <si>
-    <t>15.9</t>
-  </si>
-  <si>
-    <t>15.10</t>
-  </si>
-  <si>
-    <t>15.11</t>
-  </si>
-  <si>
-    <t>15.12</t>
-  </si>
-  <si>
-    <t>15.13</t>
-  </si>
-  <si>
-    <t>15.14</t>
-  </si>
-  <si>
-    <t>15.15</t>
-  </si>
-  <si>
-    <t>6,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UPS 내부 온도</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>###[도]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>vdc_link_volt_offset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COMMAND : Page_COMMAND == 6 [6 ~ 7],  FUNCTION CODE=0X06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SETUP : Page_Setup == 8 [8 ~ 14],  FUNCTION CODE=0X06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INTRO : Page_INTRO == 0 [0 ~ 5],  FUNCTION CODE=0X04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALL 이벤트만 기록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7초 Latch(경보, 이벤트)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>5초 Latch(경보, 이벤트)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALARM : Page_ALARM == 15 [15 ~ 20],  FUNCTION CODE=0X04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MEASUREMENT : Page_MEASURE == 20 [20 ~ 37],  FUNCTION CODE=0X04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Measure_GAIN : Page_GAIN ==38 [38 ~ 49],  FUNCTION CODE=0X04, 06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Measure OFFSET : Page_OFFSET == 50 [50 ~ 58],  FUNCTION CODE=0X04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Battery UV Primary Fault</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수정내용(일반모드)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bat First UV Volt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>80 - 280[Default = 120]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>80 - 280[Default = 120]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인버터로 절환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반표준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고효율 표준(고효율로 출고 가능성없음 인증에 필요 메모리 사용안하고 모드 고정해서 사용함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>출력 주파수로 변경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>output_frequency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OUTPUT CT ERR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>출력 CT에러</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1: fault, 0: Normal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1540,6 +1541,39 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="4"/>
     </xf>
@@ -1555,41 +1589,8 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1914,23 +1915,23 @@
     </row>
     <row r="2" spans="2:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="D2" s="80"/>
+      <c r="E2" s="20" t="s">
         <v>40</v>
-      </c>
-      <c r="D2" s="86"/>
-      <c r="E2" s="20" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="41"/>
-      <c r="C3" s="87" t="s">
-        <v>188</v>
-      </c>
-      <c r="D3" s="87"/>
-      <c r="E3" s="88"/>
+      <c r="C3" s="81" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="81"/>
+      <c r="E3" s="82"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
@@ -1943,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
@@ -1957,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
@@ -1971,7 +1972,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1982,10 +1983,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1996,50 +1997,50 @@
     </row>
     <row r="9" spans="2:6" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B9" s="29"/>
-      <c r="C9" s="75" t="s">
-        <v>186</v>
-      </c>
-      <c r="D9" s="75"/>
-      <c r="E9" s="76"/>
+      <c r="C9" s="86" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" s="86"/>
+      <c r="E9" s="87"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="82">
+      <c r="B10" s="75">
         <v>6</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="83"/>
+      <c r="B11" s="76"/>
       <c r="C11" s="8">
         <v>6.1</v>
       </c>
       <c r="D11" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="E11" s="24" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="83"/>
+      <c r="B12" s="76"/>
       <c r="C12" s="8">
         <v>6.2</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E12" s="24"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="84"/>
+      <c r="B13" s="77"/>
       <c r="C13" s="8"/>
       <c r="D13" s="23"/>
       <c r="E13" s="24"/>
@@ -2052,11 +2053,11 @@
     </row>
     <row r="15" spans="2:6" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B15" s="29"/>
-      <c r="C15" s="75" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" s="75"/>
-      <c r="E15" s="76"/>
+      <c r="C15" s="86" t="s">
+        <v>186</v>
+      </c>
+      <c r="D15" s="86"/>
+      <c r="E15" s="87"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
@@ -2069,7 +2070,7 @@
         <v>21</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
@@ -2083,7 +2084,7 @@
         <v>22</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
@@ -2094,10 +2095,10 @@
         <v>2</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
@@ -2108,13 +2109,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="63" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E19" s="64" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2125,13 +2126,13 @@
         <v>3</v>
       </c>
       <c r="D20" s="67" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="68" t="s">
-        <v>58</v>
-      </c>
       <c r="F20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2142,670 +2143,670 @@
     </row>
     <row r="22" spans="2:6" ht="28.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B22" s="34"/>
-      <c r="C22" s="89" t="s">
-        <v>192</v>
-      </c>
-      <c r="D22" s="90"/>
-      <c r="E22" s="91"/>
+      <c r="C22" s="83" t="s">
+        <v>191</v>
+      </c>
+      <c r="D22" s="84"/>
+      <c r="E22" s="85"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="1"/>
       <c r="C23" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="80">
+      <c r="B24" s="78">
         <v>15</v>
       </c>
       <c r="C24" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="26"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="78"/>
+      <c r="C25" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D25" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="E24" s="26"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="80"/>
-      <c r="C25" s="15" t="s">
+      <c r="E25" s="26"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="78"/>
+      <c r="C26" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D26" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="E25" s="26"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="80"/>
-      <c r="C26" s="15" t="s">
+      <c r="E26" s="26"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="78"/>
+      <c r="C27" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D27" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" s="26"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="78"/>
+      <c r="C28" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E28" s="26"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="78"/>
+      <c r="C29" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" s="26"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="78"/>
+      <c r="C30" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="26"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="78"/>
+      <c r="C31" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" s="26"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="78"/>
+      <c r="C32" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="E26" s="26"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="80"/>
-      <c r="C27" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E27" s="26"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="80"/>
-      <c r="C28" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" s="26"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="80"/>
-      <c r="C29" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E29" s="26"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="80"/>
-      <c r="C30" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="D30" s="25" t="s">
+      <c r="E32" s="26"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="78"/>
+      <c r="C33" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="26"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34" s="78"/>
+      <c r="C34" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" s="26"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="78"/>
+      <c r="C35" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="26"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="78"/>
+      <c r="C36" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="E36" s="26"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="78"/>
+      <c r="C37" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D37" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="E30" s="26"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="80"/>
-      <c r="C31" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" s="26"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="80"/>
-      <c r="C32" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="E32" s="26"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="80"/>
-      <c r="C33" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" s="26"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B34" s="80"/>
-      <c r="C34" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" s="26"/>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35" s="80"/>
-      <c r="C35" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="E35" s="26"/>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="80"/>
-      <c r="C36" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="E36" s="26"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="80"/>
-      <c r="C37" s="15" t="s">
+      <c r="E37" s="26"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="78"/>
+      <c r="C38" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="D37" s="25" t="s">
+      <c r="D38" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="E37" s="26"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="80"/>
-      <c r="C38" s="15" t="s">
+      <c r="E38" s="26"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39" s="91"/>
+      <c r="C39" s="15" t="s">
         <v>180</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="E38" s="26"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="81"/>
-      <c r="C39" s="15" t="s">
-        <v>181</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="26"/>
       <c r="F39" s="35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="10"/>
       <c r="C40" s="38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D40" s="33" t="s">
         <v>3</v>
       </c>
       <c r="E40" s="39" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="82">
+      <c r="B41" s="75">
         <v>16</v>
       </c>
       <c r="C41" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B42" s="78"/>
+      <c r="C42" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="D42" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="E42" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="E41" s="28" t="s">
+      <c r="F42" s="35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B43" s="78"/>
+      <c r="C43" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F43" s="36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B44" s="78"/>
+      <c r="C44" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="D44" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="51" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B45" s="78"/>
+      <c r="C45" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="F41" s="36" t="s">
+      <c r="E45" s="51" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B46" s="78"/>
+      <c r="C46" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F46" s="36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B47" s="78"/>
+      <c r="C47" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47" s="35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B48" s="78"/>
+      <c r="C48" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F48" s="35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B49" s="78"/>
+      <c r="C49" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F49" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B50" s="78"/>
+      <c r="C50" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="D50" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="E50" s="51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B51" s="78"/>
+      <c r="C51" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F51" s="35" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="80"/>
-      <c r="C42" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="D42" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="E42" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F42" s="35" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B43" s="80"/>
-      <c r="C43" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="D43" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F43" s="36" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B44" s="80"/>
-      <c r="C44" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="D44" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="E44" s="51" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B45" s="80"/>
-      <c r="C45" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="D45" s="50" t="s">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B52" s="78"/>
+      <c r="C52" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D52" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E52" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F52" s="36" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B53" s="76"/>
+      <c r="C53" s="54" t="s">
+        <v>161</v>
+      </c>
+      <c r="D53" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="E45" s="51" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="80"/>
-      <c r="C46" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D46" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F46" s="36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="80"/>
-      <c r="C47" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F47" s="35" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="80"/>
-      <c r="C48" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="D48" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F48" s="35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="80"/>
-      <c r="C49" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D49" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="E49" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F49" s="36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B50" s="80"/>
-      <c r="C50" s="49" t="s">
-        <v>159</v>
-      </c>
-      <c r="D50" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="E50" s="51" t="s">
+      <c r="E53" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="F53" s="36"/>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B54" s="76"/>
+      <c r="C54" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" s="28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B55" s="76"/>
+      <c r="C55" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E55" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F55" s="35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B56" s="77"/>
+      <c r="C56" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="D56" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="E56" s="53" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="80"/>
-      <c r="C51" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="D51" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F51" s="35" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="80"/>
-      <c r="C52" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="D52" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F52" s="36" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B53" s="83"/>
-      <c r="C53" s="54" t="s">
-        <v>162</v>
-      </c>
-      <c r="D53" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="E53" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="F53" s="36"/>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B54" s="83"/>
-      <c r="C54" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="D54" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="E54" s="28" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="83"/>
-      <c r="C55" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="D55" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="E55" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F55" s="35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B56" s="84"/>
-      <c r="C56" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="D56" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="E56" s="53" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="1"/>
       <c r="C57" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B58" s="75">
+        <v>17</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E58" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="F58" s="36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B59" s="76"/>
+      <c r="C59" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D59" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E59" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" s="35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B60" s="76"/>
+      <c r="C60" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E60" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F60" s="35" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B61" s="76"/>
+      <c r="C61" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D61" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F61" s="36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B62" s="76"/>
+      <c r="C62" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D62" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="E62" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F62" s="36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B63" s="76"/>
+      <c r="C63" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D63" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="E63" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63" s="36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B64" s="76"/>
+      <c r="C64" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="D64" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="E64" s="59" t="s">
+        <v>74</v>
+      </c>
+      <c r="F64" s="60" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B65" s="76"/>
+      <c r="C65" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D65" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="E65" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F65" s="36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B66" s="76"/>
+      <c r="C66" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E66" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F66" s="35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B67" s="76"/>
+      <c r="C67" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D67" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F67" s="35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B68" s="76"/>
+      <c r="C68" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D68" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E68" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F68" s="35" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B69" s="76"/>
+      <c r="C69" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D69" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F69" s="35" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B70" s="76"/>
+      <c r="C70" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D70" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B71" s="76"/>
+      <c r="C71" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D71" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E71" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F71" s="35" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B72" s="76"/>
+      <c r="C72" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D72" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D57" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B58" s="82">
-        <v>17</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="D58" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="E58" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="F58" s="36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="83"/>
-      <c r="C59" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="E59" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F59" s="35" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B60" s="83"/>
-      <c r="C60" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="E60" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F60" s="35" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="83"/>
-      <c r="C61" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="D61" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E61" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F61" s="36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="83"/>
-      <c r="C62" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="D62" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="E62" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F62" s="36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B63" s="83"/>
-      <c r="C63" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="E63" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F63" s="36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B64" s="83"/>
-      <c r="C64" s="57" t="s">
-        <v>141</v>
-      </c>
-      <c r="D64" s="58" t="s">
-        <v>196</v>
-      </c>
-      <c r="E64" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="F64" s="60" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B65" s="83"/>
-      <c r="C65" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="D65" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E65" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F65" s="36" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B66" s="83"/>
-      <c r="C66" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="D66" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="E66" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F66" s="35" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B67" s="83"/>
-      <c r="C67" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="D67" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E67" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F67" s="35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B68" s="83"/>
-      <c r="C68" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="D68" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="E68" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F68" s="35" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B69" s="83"/>
-      <c r="C69" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D69" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="E69" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F69" s="35" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="83"/>
-      <c r="C70" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="D70" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="E70" s="28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B71" s="83"/>
-      <c r="C71" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="D71" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E71" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F71" s="35" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B72" s="83"/>
-      <c r="C72" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="D72" s="27" t="s">
-        <v>85</v>
-      </c>
       <c r="E72" s="28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="85"/>
+      <c r="B73" s="79"/>
       <c r="C73" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D73" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="E73" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="D73" s="30" t="s">
+      <c r="F73" s="35" t="s">
         <v>206</v>
-      </c>
-      <c r="E73" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="F73" s="35" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2816,11 +2817,11 @@
     </row>
     <row r="75" spans="2:6" ht="28.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B75" s="29"/>
-      <c r="C75" s="75" t="s">
-        <v>193</v>
-      </c>
-      <c r="D75" s="75"/>
-      <c r="E75" s="76"/>
+      <c r="C75" s="86" t="s">
+        <v>192</v>
+      </c>
+      <c r="D75" s="86"/>
+      <c r="E75" s="87"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="4">
@@ -2833,7 +2834,7 @@
         <v>4</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.3">
@@ -2847,7 +2848,7 @@
         <v>5</v>
       </c>
       <c r="E77" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
@@ -2861,7 +2862,7 @@
         <v>6</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
@@ -2875,7 +2876,7 @@
         <v>7</v>
       </c>
       <c r="E79" s="24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
@@ -2889,7 +2890,7 @@
         <v>8</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
@@ -2903,7 +2904,7 @@
         <v>9</v>
       </c>
       <c r="E81" s="24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
@@ -2917,7 +2918,7 @@
         <v>10</v>
       </c>
       <c r="E82" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
@@ -2931,7 +2932,7 @@
         <v>11</v>
       </c>
       <c r="E83" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
@@ -2945,7 +2946,7 @@
         <v>12</v>
       </c>
       <c r="E84" s="47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
@@ -2959,7 +2960,7 @@
         <v>13</v>
       </c>
       <c r="E85" s="47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
@@ -2970,10 +2971,10 @@
         <v>10</v>
       </c>
       <c r="D86" s="42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E86" s="48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87" spans="2:7" s="74" customFormat="1" x14ac:dyDescent="0.3">
@@ -2984,16 +2985,16 @@
         <v>11</v>
       </c>
       <c r="D87" s="72" t="s">
+        <v>51</v>
+      </c>
+      <c r="E87" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="E87" s="73" t="s">
-        <v>53</v>
-      </c>
       <c r="F87" s="69" t="s">
+        <v>203</v>
+      </c>
+      <c r="G87" s="74" t="s">
         <v>204</v>
-      </c>
-      <c r="G87" s="74" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
@@ -3004,10 +3005,10 @@
         <v>12</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E88" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
@@ -3018,10 +3019,10 @@
         <v>13</v>
       </c>
       <c r="D89" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="90" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3032,10 +3033,10 @@
         <v>14</v>
       </c>
       <c r="D90" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="E90" s="26" t="s">
         <v>183</v>
-      </c>
-      <c r="E90" s="26" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="91" spans="2:7" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3046,11 +3047,11 @@
     </row>
     <row r="92" spans="2:7" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B92" s="29"/>
-      <c r="C92" s="77" t="s">
-        <v>194</v>
-      </c>
-      <c r="D92" s="78"/>
-      <c r="E92" s="79"/>
+      <c r="C92" s="88" t="s">
+        <v>193</v>
+      </c>
+      <c r="D92" s="89"/>
+      <c r="E92" s="90"/>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B93" s="1">
@@ -3060,10 +3061,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E93" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
@@ -3077,7 +3078,7 @@
         <v>14</v>
       </c>
       <c r="E94" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
@@ -3091,7 +3092,7 @@
         <v>15</v>
       </c>
       <c r="E95" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
@@ -3105,7 +3106,7 @@
         <v>16</v>
       </c>
       <c r="E96" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.3">
@@ -3119,7 +3120,7 @@
         <v>17</v>
       </c>
       <c r="E97" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.3">
@@ -3133,7 +3134,7 @@
         <v>18</v>
       </c>
       <c r="E98" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.3">
@@ -3147,7 +3148,7 @@
         <v>19</v>
       </c>
       <c r="E99" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.3">
@@ -3159,7 +3160,7 @@
       </c>
       <c r="D100" s="23"/>
       <c r="E100" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.3">
@@ -3173,7 +3174,7 @@
         <v>20</v>
       </c>
       <c r="E101" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.3">
@@ -3189,11 +3190,11 @@
     <row r="103" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="104" spans="2:5" ht="27" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B104" s="29"/>
-      <c r="C104" s="75" t="s">
-        <v>195</v>
-      </c>
-      <c r="D104" s="75"/>
-      <c r="E104" s="76"/>
+      <c r="C104" s="86" t="s">
+        <v>194</v>
+      </c>
+      <c r="D104" s="86"/>
+      <c r="E104" s="87"/>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B105" s="4">
@@ -3203,10 +3204,10 @@
         <v>0</v>
       </c>
       <c r="D105" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E105" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.3">
@@ -3217,10 +3218,10 @@
         <v>1</v>
       </c>
       <c r="D106" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E106" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.3">
@@ -3231,10 +3232,10 @@
         <v>2</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E107" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.3">
@@ -3245,10 +3246,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E108" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.3">
@@ -3259,10 +3260,10 @@
         <v>4</v>
       </c>
       <c r="D109" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E109" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.3">
@@ -3273,10 +3274,10 @@
         <v>5</v>
       </c>
       <c r="D110" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E110" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.3">
@@ -3287,10 +3288,10 @@
         <v>6</v>
       </c>
       <c r="D111" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E111" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.3">
@@ -3302,7 +3303,7 @@
       </c>
       <c r="D112" s="23"/>
       <c r="E112" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="113" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3313,15 +3314,20 @@
         <v>8</v>
       </c>
       <c r="D113" s="44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E113" s="45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="114" spans="2:5" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="B24:B39"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="B41:B56"/>
     <mergeCell ref="B58:B73"/>
@@ -3329,11 +3335,6 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="B24:B39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
